--- a/raw/Timetable_2026Autumn_2026EE.xlsx
+++ b/raw/Timetable_2026Autumn_2026EE.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30602"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12C4DEC-AD15-40ED-A8DF-E1C6DB92D88A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2263EDD-971D-4C99-9956-7B50367585DB}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026EE1" sheetId="2" r:id="rId1"/>
@@ -303,13 +303,13 @@
     <t>8       Oct.</t>
   </si>
   <si>
+    <t>9       Oct.</t>
+  </si>
+  <si>
+    <t>10       Oct.</t>
+  </si>
+  <si>
     <t>B411</t>
-  </si>
-  <si>
-    <t>9       Oct.</t>
-  </si>
-  <si>
-    <t>10       Oct.</t>
   </si>
   <si>
     <t>11       Oct.</t>
@@ -968,6 +968,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -998,12 +1025,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1017,27 +1038,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1388,81 +1388,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29" t="s">
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="41" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29" t="s">
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29" t="s">
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="39">
+      <c r="A4" s="36">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1504,7 +1504,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="39"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="39"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -1624,7 +1624,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="39"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -1672,7 +1672,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="39"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
@@ -1728,7 +1728,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="39"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
@@ -1780,7 +1780,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="39"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
@@ -1824,7 +1824,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="37">
         <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -1872,7 +1872,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="40"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
@@ -1930,7 +1930,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="12" t="s">
         <v>51</v>
       </c>
@@ -1985,7 +1985,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="U14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="12" t="s">
         <v>56</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="U15" s="15"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="12" t="s">
         <v>57</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="12" t="s">
         <v>58</v>
       </c>
@@ -2119,7 +2119,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="39">
+      <c r="A18" s="36">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2152,7 +2152,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
@@ -2195,7 +2195,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
@@ -2250,7 +2250,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="39"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
@@ -2349,7 +2349,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="39"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="16" t="s">
         <v>65</v>
       </c>
@@ -2388,7 +2388,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="40">
+      <c r="A25" s="37">
         <v>4</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -2421,7 +2421,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="40"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="12" t="s">
         <v>67</v>
       </c>
@@ -2464,7 +2464,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="40"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="12" t="s">
         <v>68</v>
       </c>
@@ -2519,7 +2519,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="40"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="12" t="s">
         <v>69</v>
       </c>
@@ -2550,90 +2550,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="40"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="20" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="32"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="41"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="40"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="20" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="44"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="40"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="38"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="47"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="39">
+      <c r="A32" s="36">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2678,7 +2678,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="39"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="39"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
@@ -2764,117 +2764,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="39"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="32"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="41"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="39"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="22" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="35"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="44"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="39"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="22" t="s">
         <v>81</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="35"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="44"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="39"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="22" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="35"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="44"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="40">
+      <c r="A39" s="37">
         <v>6</v>
       </c>
       <c r="B39" s="22" t="s">
@@ -2883,105 +2883,93 @@
       <c r="C39" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="35"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="44"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="40"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="22" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="33"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="35"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="44"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="40"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="22" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="38"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="47"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="40"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="23" t="s">
         <v>86</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>87</v>
-      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="12" t="s">
         <v>16</v>
       </c>
@@ -3000,9 +2988,9 @@
       <c r="U42" s="15"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="40"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>36</v>
@@ -3041,9 +3029,9 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="40"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>41</v>
@@ -3054,12 +3042,24 @@
       <c r="G44" s="16"/>
       <c r="H44" s="18"/>
       <c r="I44" s="19"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="19"/>
+      <c r="J44" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M44" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N44" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O44" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="P44" s="16"/>
       <c r="Q44" s="18"/>
       <c r="R44" s="19"/>
@@ -3068,7 +3068,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="40"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="23" t="s">
         <v>90</v>
       </c>
@@ -3095,7 +3095,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="39">
+      <c r="A46" s="36">
         <v>7</v>
       </c>
       <c r="B46" s="25" t="s">
@@ -3140,7 +3140,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="39"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="25" t="s">
         <v>92</v>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="39"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="25" t="s">
         <v>93</v>
       </c>
@@ -3226,7 +3226,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="39"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="25" t="s">
         <v>94</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>48</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>47</v>
@@ -3249,7 +3249,7 @@
         <v>48</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>16</v>
@@ -3269,7 +3269,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="39"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
@@ -3310,7 +3310,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="39"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="25" t="s">
         <v>96</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="39"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="25" t="s">
         <v>97</v>
       </c>
@@ -3372,7 +3372,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="40">
+      <c r="A53" s="37">
         <v>8</v>
       </c>
       <c r="B53" s="23" t="s">
@@ -3417,7 +3417,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="40"/>
+      <c r="A54" s="37"/>
       <c r="B54" s="23" t="s">
         <v>99</v>
       </c>
@@ -3460,7 +3460,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="40"/>
+      <c r="A55" s="37"/>
       <c r="B55" s="23" t="s">
         <v>100</v>
       </c>
@@ -3515,7 +3515,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="40"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="23" t="s">
         <v>101</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>48</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G56" s="12" t="s">
         <v>47</v>
@@ -3538,7 +3538,7 @@
         <v>48</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J56" s="12" t="s">
         <v>16</v>
@@ -3558,7 +3558,7 @@
       <c r="U56" s="15"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="40"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="23" t="s">
         <v>102</v>
       </c>
@@ -3601,7 +3601,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="40"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="23" t="s">
         <v>103</v>
       </c>
@@ -3636,7 +3636,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="40"/>
+      <c r="A59" s="37"/>
       <c r="B59" s="23" t="s">
         <v>104</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="39">
+      <c r="A60" s="36">
         <v>9</v>
       </c>
       <c r="B60" s="25" t="s">
@@ -3708,7 +3708,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="39"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="25" t="s">
         <v>106</v>
       </c>
@@ -3751,7 +3751,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="39"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="25" t="s">
         <v>107</v>
       </c>
@@ -3806,7 +3806,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="39"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="25" t="s">
         <v>108</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>48</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>47</v>
@@ -3829,7 +3829,7 @@
         <v>48</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J63" s="6" t="s">
         <v>16</v>
@@ -3849,7 +3849,7 @@
       <c r="U63" s="26"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="39"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="25" t="s">
         <v>109</v>
       </c>
@@ -3892,7 +3892,7 @@
       <c r="U64" s="26"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="39"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="25" t="s">
         <v>110</v>
       </c>
@@ -3927,7 +3927,7 @@
       <c r="U65" s="26"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="39"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="25" t="s">
         <v>111</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="U66" s="26"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="40">
+      <c r="A67" s="37">
         <v>10</v>
       </c>
       <c r="B67" s="23" t="s">
@@ -3999,7 +3999,7 @@
       <c r="U67" s="27"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="40"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="23" t="s">
         <v>113</v>
       </c>
@@ -4042,7 +4042,7 @@
       <c r="U68" s="27"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="40"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="23" t="s">
         <v>114</v>
       </c>
@@ -4085,7 +4085,7 @@
       <c r="U69" s="27"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="40"/>
+      <c r="A70" s="37"/>
       <c r="B70" s="23" t="s">
         <v>115</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>48</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G70" s="12" t="s">
         <v>47</v>
@@ -4108,7 +4108,7 @@
         <v>48</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J70" s="12" t="s">
         <v>16</v>
@@ -4128,7 +4128,7 @@
       <c r="U70" s="27"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="40"/>
+      <c r="A71" s="37"/>
       <c r="B71" s="23" t="s">
         <v>116</v>
       </c>
@@ -4171,7 +4171,7 @@
       <c r="U71" s="27"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="40"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="23" t="s">
         <v>117</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="U72" s="27"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="40"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="23" t="s">
         <v>118</v>
       </c>
@@ -4225,7 +4225,7 @@
       <c r="U73" s="27"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="39">
+      <c r="A74" s="36">
         <v>11</v>
       </c>
       <c r="B74" s="25" t="s">
@@ -4270,7 +4270,7 @@
       <c r="U74" s="26"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="39"/>
+      <c r="A75" s="36"/>
       <c r="B75" s="25" t="s">
         <v>120</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="U75" s="26"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="39"/>
+      <c r="A76" s="36"/>
       <c r="B76" s="25" t="s">
         <v>121</v>
       </c>
@@ -4368,7 +4368,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="39"/>
+      <c r="A77" s="36"/>
       <c r="B77" s="25" t="s">
         <v>122</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>48</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>47</v>
@@ -4391,7 +4391,7 @@
         <v>48</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>16</v>
@@ -4411,7 +4411,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="39"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="25" t="s">
         <v>123</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="39"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="25" t="s">
         <v>124</v>
       </c>
@@ -4481,7 +4481,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="39"/>
+      <c r="A80" s="36"/>
       <c r="B80" s="25" t="s">
         <v>125</v>
       </c>
@@ -4508,7 +4508,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="40">
+      <c r="A81" s="37">
         <v>12</v>
       </c>
       <c r="B81" s="23" t="s">
@@ -4553,7 +4553,7 @@
       <c r="U81" s="15"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="40"/>
+      <c r="A82" s="37"/>
       <c r="B82" s="23" t="s">
         <v>127</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="U82" s="15"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="40"/>
+      <c r="A83" s="37"/>
       <c r="B83" s="23" t="s">
         <v>128</v>
       </c>
@@ -4651,7 +4651,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="40"/>
+      <c r="A84" s="37"/>
       <c r="B84" s="23" t="s">
         <v>131</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>48</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>47</v>
@@ -4674,7 +4674,7 @@
         <v>48</v>
       </c>
       <c r="I84" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J84" s="12" t="s">
         <v>16</v>
@@ -4694,7 +4694,7 @@
       <c r="U84" s="15"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="40"/>
+      <c r="A85" s="37"/>
       <c r="B85" s="23" t="s">
         <v>132</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="U85" s="15"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="40"/>
+      <c r="A86" s="37"/>
       <c r="B86" s="23" t="s">
         <v>133</v>
       </c>
@@ -4772,7 +4772,7 @@
       <c r="U86" s="15"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="40"/>
+      <c r="A87" s="37"/>
       <c r="B87" s="23" t="s">
         <v>134</v>
       </c>
@@ -4799,7 +4799,7 @@
       <c r="U87" s="15"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="39">
+      <c r="A88" s="36">
         <v>13</v>
       </c>
       <c r="B88" s="25" t="s">
@@ -4844,7 +4844,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="39"/>
+      <c r="A89" s="36"/>
       <c r="B89" s="25" t="s">
         <v>136</v>
       </c>
@@ -4887,7 +4887,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="39"/>
+      <c r="A90" s="36"/>
       <c r="B90" s="25" t="s">
         <v>137</v>
       </c>
@@ -4942,7 +4942,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="39"/>
+      <c r="A91" s="36"/>
       <c r="B91" s="25" t="s">
         <v>138</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>48</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>47</v>
@@ -4965,7 +4965,7 @@
         <v>48</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J91" s="6" t="s">
         <v>16</v>
@@ -4985,7 +4985,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="39"/>
+      <c r="A92" s="36"/>
       <c r="B92" s="25" t="s">
         <v>139</v>
       </c>
@@ -5028,7 +5028,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="39"/>
+      <c r="A93" s="36"/>
       <c r="B93" s="25" t="s">
         <v>140</v>
       </c>
@@ -5063,7 +5063,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="39"/>
+      <c r="A94" s="36"/>
       <c r="B94" s="25" t="s">
         <v>141</v>
       </c>
@@ -5090,7 +5090,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="40">
+      <c r="A95" s="37">
         <v>14</v>
       </c>
       <c r="B95" s="23" t="s">
@@ -5135,7 +5135,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="40"/>
+      <c r="A96" s="37"/>
       <c r="B96" s="23" t="s">
         <v>143</v>
       </c>
@@ -5178,7 +5178,7 @@
       <c r="U96" s="15"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="40"/>
+      <c r="A97" s="37"/>
       <c r="B97" s="23" t="s">
         <v>144</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="40"/>
+      <c r="A98" s="37"/>
       <c r="B98" s="23" t="s">
         <v>145</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>48</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>47</v>
@@ -5256,7 +5256,7 @@
         <v>48</v>
       </c>
       <c r="I98" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J98" s="12" t="s">
         <v>16</v>
@@ -5276,7 +5276,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="40"/>
+      <c r="A99" s="37"/>
       <c r="B99" s="23" t="s">
         <v>146</v>
       </c>
@@ -5319,7 +5319,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="40"/>
+      <c r="A100" s="37"/>
       <c r="B100" s="23" t="s">
         <v>147</v>
       </c>
@@ -5346,7 +5346,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="40"/>
+      <c r="A101" s="37"/>
       <c r="B101" s="23" t="s">
         <v>148</v>
       </c>
@@ -5373,7 +5373,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="39">
+      <c r="A102" s="36">
         <v>15</v>
       </c>
       <c r="B102" s="25" t="s">
@@ -5418,7 +5418,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="39"/>
+      <c r="A103" s="36"/>
       <c r="B103" s="25" t="s">
         <v>150</v>
       </c>
@@ -5461,7 +5461,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="39"/>
+      <c r="A104" s="36"/>
       <c r="B104" s="25" t="s">
         <v>151</v>
       </c>
@@ -5516,7 +5516,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="39"/>
+      <c r="A105" s="36"/>
       <c r="B105" s="25" t="s">
         <v>152</v>
       </c>
@@ -5530,7 +5530,7 @@
         <v>48</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>47</v>
@@ -5539,7 +5539,7 @@
         <v>48</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J105" s="6" t="s">
         <v>16</v>
@@ -5559,7 +5559,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="39"/>
+      <c r="A106" s="36"/>
       <c r="B106" s="25" t="s">
         <v>153</v>
       </c>
@@ -5602,7 +5602,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="39"/>
+      <c r="A107" s="36"/>
       <c r="B107" s="25" t="s">
         <v>154</v>
       </c>
@@ -5637,7 +5637,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="39"/>
+      <c r="A108" s="36"/>
       <c r="B108" s="25" t="s">
         <v>155</v>
       </c>
@@ -5664,7 +5664,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="40">
+      <c r="A109" s="37">
         <v>16</v>
       </c>
       <c r="B109" s="23" t="s">
@@ -5709,7 +5709,7 @@
       <c r="U109" s="27"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="40"/>
+      <c r="A110" s="37"/>
       <c r="B110" s="23" t="s">
         <v>157</v>
       </c>
@@ -5752,7 +5752,7 @@
       <c r="U110" s="27"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="40"/>
+      <c r="A111" s="37"/>
       <c r="B111" s="23" t="s">
         <v>158</v>
       </c>
@@ -5807,7 +5807,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="40"/>
+      <c r="A112" s="37"/>
       <c r="B112" s="23" t="s">
         <v>159</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>48</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G112" s="12" t="s">
         <v>47</v>
@@ -5830,7 +5830,7 @@
         <v>48</v>
       </c>
       <c r="I112" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>16</v>
@@ -5850,7 +5850,7 @@
       <c r="U112" s="27"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="40"/>
+      <c r="A113" s="37"/>
       <c r="B113" s="23" t="s">
         <v>160</v>
       </c>
@@ -5893,7 +5893,7 @@
       <c r="U113" s="27"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="40"/>
+      <c r="A114" s="37"/>
       <c r="B114" s="23" t="s">
         <v>161</v>
       </c>
@@ -5920,7 +5920,7 @@
       <c r="U114" s="27"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="40"/>
+      <c r="A115" s="37"/>
       <c r="B115" s="23" t="s">
         <v>162</v>
       </c>
@@ -5947,7 +5947,7 @@
       <c r="U115" s="27"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="39">
+      <c r="A116" s="36">
         <v>17</v>
       </c>
       <c r="B116" s="25" t="s">
@@ -5990,7 +5990,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="39"/>
+      <c r="A117" s="36"/>
       <c r="B117" s="25" t="s">
         <v>164</v>
       </c>
@@ -6019,7 +6019,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="39"/>
+      <c r="A118" s="36"/>
       <c r="B118" s="25" t="s">
         <v>165</v>
       </c>
@@ -6072,7 +6072,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="39"/>
+      <c r="A119" s="36"/>
       <c r="B119" s="25" t="s">
         <v>166</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>48</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>47</v>
@@ -6095,7 +6095,7 @@
         <v>48</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J119" s="6"/>
       <c r="K119" s="8"/>
@@ -6113,7 +6113,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="39"/>
+      <c r="A120" s="36"/>
       <c r="B120" s="25" t="s">
         <v>167</v>
       </c>
@@ -6156,7 +6156,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="39"/>
+      <c r="A121" s="36"/>
       <c r="B121" s="25" t="s">
         <v>168</v>
       </c>
@@ -6183,7 +6183,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="39"/>
+      <c r="A122" s="36"/>
       <c r="B122" s="25" t="s">
         <v>169</v>
       </c>
@@ -6210,7 +6210,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="40">
+      <c r="A123" s="37">
         <v>18</v>
       </c>
       <c r="B123" s="23" t="s">
@@ -6219,191 +6219,191 @@
       <c r="C123" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="46" t="s">
+      <c r="D123" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="47"/>
-      <c r="L123" s="47"/>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
-      <c r="O123" s="47"/>
-      <c r="P123" s="47"/>
-      <c r="Q123" s="47"/>
-      <c r="R123" s="47"/>
-      <c r="S123" s="47"/>
-      <c r="T123" s="47"/>
-      <c r="U123" s="48"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="30"/>
+      <c r="K123" s="30"/>
+      <c r="L123" s="30"/>
+      <c r="M123" s="30"/>
+      <c r="N123" s="30"/>
+      <c r="O123" s="30"/>
+      <c r="P123" s="30"/>
+      <c r="Q123" s="30"/>
+      <c r="R123" s="30"/>
+      <c r="S123" s="30"/>
+      <c r="T123" s="30"/>
+      <c r="U123" s="31"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="40"/>
+      <c r="A124" s="37"/>
       <c r="B124" s="23" t="s">
         <v>172</v>
       </c>
       <c r="C124" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="49"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="49"/>
-      <c r="H124" s="49"/>
-      <c r="I124" s="49"/>
-      <c r="J124" s="49"/>
-      <c r="K124" s="49"/>
-      <c r="L124" s="49"/>
-      <c r="M124" s="49"/>
-      <c r="N124" s="49"/>
-      <c r="O124" s="49"/>
-      <c r="P124" s="49"/>
-      <c r="Q124" s="49"/>
-      <c r="R124" s="49"/>
-      <c r="S124" s="49"/>
-      <c r="T124" s="49"/>
-      <c r="U124" s="50"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="32"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+      <c r="I124" s="32"/>
+      <c r="J124" s="32"/>
+      <c r="K124" s="32"/>
+      <c r="L124" s="32"/>
+      <c r="M124" s="32"/>
+      <c r="N124" s="32"/>
+      <c r="O124" s="32"/>
+      <c r="P124" s="32"/>
+      <c r="Q124" s="32"/>
+      <c r="R124" s="32"/>
+      <c r="S124" s="32"/>
+      <c r="T124" s="32"/>
+      <c r="U124" s="33"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="40"/>
+      <c r="A125" s="37"/>
       <c r="B125" s="23" t="s">
         <v>173</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="49"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="49"/>
-      <c r="J125" s="49"/>
-      <c r="K125" s="49"/>
-      <c r="L125" s="49"/>
-      <c r="M125" s="49"/>
-      <c r="N125" s="49"/>
-      <c r="O125" s="49"/>
-      <c r="P125" s="49"/>
-      <c r="Q125" s="49"/>
-      <c r="R125" s="49"/>
-      <c r="S125" s="49"/>
-      <c r="T125" s="49"/>
-      <c r="U125" s="50"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
+      <c r="F125" s="32"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+      <c r="I125" s="32"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="32"/>
+      <c r="L125" s="32"/>
+      <c r="M125" s="32"/>
+      <c r="N125" s="32"/>
+      <c r="O125" s="32"/>
+      <c r="P125" s="32"/>
+      <c r="Q125" s="32"/>
+      <c r="R125" s="32"/>
+      <c r="S125" s="32"/>
+      <c r="T125" s="32"/>
+      <c r="U125" s="33"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="40"/>
+      <c r="A126" s="37"/>
       <c r="B126" s="23" t="s">
         <v>174</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="49"/>
-      <c r="J126" s="49"/>
-      <c r="K126" s="49"/>
-      <c r="L126" s="49"/>
-      <c r="M126" s="49"/>
-      <c r="N126" s="49"/>
-      <c r="O126" s="49"/>
-      <c r="P126" s="49"/>
-      <c r="Q126" s="49"/>
-      <c r="R126" s="49"/>
-      <c r="S126" s="49"/>
-      <c r="T126" s="49"/>
-      <c r="U126" s="50"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
+      <c r="J126" s="32"/>
+      <c r="K126" s="32"/>
+      <c r="L126" s="32"/>
+      <c r="M126" s="32"/>
+      <c r="N126" s="32"/>
+      <c r="O126" s="32"/>
+      <c r="P126" s="32"/>
+      <c r="Q126" s="32"/>
+      <c r="R126" s="32"/>
+      <c r="S126" s="32"/>
+      <c r="T126" s="32"/>
+      <c r="U126" s="33"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="40"/>
+      <c r="A127" s="37"/>
       <c r="B127" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C127" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="49"/>
-      <c r="J127" s="49"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="49"/>
-      <c r="M127" s="49"/>
-      <c r="N127" s="49"/>
-      <c r="O127" s="49"/>
-      <c r="P127" s="49"/>
-      <c r="Q127" s="49"/>
-      <c r="R127" s="49"/>
-      <c r="S127" s="49"/>
-      <c r="T127" s="49"/>
-      <c r="U127" s="50"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="32"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+      <c r="I127" s="32"/>
+      <c r="J127" s="32"/>
+      <c r="K127" s="32"/>
+      <c r="L127" s="32"/>
+      <c r="M127" s="32"/>
+      <c r="N127" s="32"/>
+      <c r="O127" s="32"/>
+      <c r="P127" s="32"/>
+      <c r="Q127" s="32"/>
+      <c r="R127" s="32"/>
+      <c r="S127" s="32"/>
+      <c r="T127" s="32"/>
+      <c r="U127" s="33"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="40"/>
+      <c r="A128" s="37"/>
       <c r="B128" s="23" t="s">
         <v>176</v>
       </c>
       <c r="C128" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="49"/>
-      <c r="F128" s="49"/>
-      <c r="G128" s="49"/>
-      <c r="H128" s="49"/>
-      <c r="I128" s="49"/>
-      <c r="J128" s="49"/>
-      <c r="K128" s="49"/>
-      <c r="L128" s="49"/>
-      <c r="M128" s="49"/>
-      <c r="N128" s="49"/>
-      <c r="O128" s="49"/>
-      <c r="P128" s="49"/>
-      <c r="Q128" s="49"/>
-      <c r="R128" s="49"/>
-      <c r="S128" s="49"/>
-      <c r="T128" s="49"/>
-      <c r="U128" s="50"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="32"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+      <c r="I128" s="32"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="32"/>
+      <c r="L128" s="32"/>
+      <c r="M128" s="32"/>
+      <c r="N128" s="32"/>
+      <c r="O128" s="32"/>
+      <c r="P128" s="32"/>
+      <c r="Q128" s="32"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="32"/>
+      <c r="T128" s="32"/>
+      <c r="U128" s="33"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="40"/>
+      <c r="A129" s="37"/>
       <c r="B129" s="23" t="s">
         <v>177</v>
       </c>
       <c r="C129" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="49"/>
-      <c r="F129" s="49"/>
-      <c r="G129" s="49"/>
-      <c r="H129" s="49"/>
-      <c r="I129" s="49"/>
-      <c r="J129" s="49"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="49"/>
-      <c r="M129" s="49"/>
-      <c r="N129" s="49"/>
-      <c r="O129" s="49"/>
-      <c r="P129" s="49"/>
-      <c r="Q129" s="49"/>
-      <c r="R129" s="49"/>
-      <c r="S129" s="49"/>
-      <c r="T129" s="49"/>
-      <c r="U129" s="50"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="32"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="32"/>
+      <c r="H129" s="32"/>
+      <c r="I129" s="32"/>
+      <c r="J129" s="32"/>
+      <c r="K129" s="32"/>
+      <c r="L129" s="32"/>
+      <c r="M129" s="32"/>
+      <c r="N129" s="32"/>
+      <c r="O129" s="32"/>
+      <c r="P129" s="32"/>
+      <c r="Q129" s="32"/>
+      <c r="R129" s="32"/>
+      <c r="S129" s="32"/>
+      <c r="T129" s="32"/>
+      <c r="U129" s="33"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="39">
+      <c r="A130" s="36">
         <v>19</v>
       </c>
       <c r="B130" s="25" t="s">
@@ -6412,186 +6412,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="49"/>
-      <c r="F130" s="49"/>
-      <c r="G130" s="49"/>
-      <c r="H130" s="49"/>
-      <c r="I130" s="49"/>
-      <c r="J130" s="49"/>
-      <c r="K130" s="49"/>
-      <c r="L130" s="49"/>
-      <c r="M130" s="49"/>
-      <c r="N130" s="49"/>
-      <c r="O130" s="49"/>
-      <c r="P130" s="49"/>
-      <c r="Q130" s="49"/>
-      <c r="R130" s="49"/>
-      <c r="S130" s="49"/>
-      <c r="T130" s="49"/>
-      <c r="U130" s="50"/>
+      <c r="D130" s="32"/>
+      <c r="E130" s="32"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="32"/>
+      <c r="H130" s="32"/>
+      <c r="I130" s="32"/>
+      <c r="J130" s="32"/>
+      <c r="K130" s="32"/>
+      <c r="L130" s="32"/>
+      <c r="M130" s="32"/>
+      <c r="N130" s="32"/>
+      <c r="O130" s="32"/>
+      <c r="P130" s="32"/>
+      <c r="Q130" s="32"/>
+      <c r="R130" s="32"/>
+      <c r="S130" s="32"/>
+      <c r="T130" s="32"/>
+      <c r="U130" s="33"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="39"/>
+      <c r="A131" s="36"/>
       <c r="B131" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="49"/>
-      <c r="E131" s="49"/>
-      <c r="F131" s="49"/>
-      <c r="G131" s="49"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="49"/>
-      <c r="J131" s="49"/>
-      <c r="K131" s="49"/>
-      <c r="L131" s="49"/>
-      <c r="M131" s="49"/>
-      <c r="N131" s="49"/>
-      <c r="O131" s="49"/>
-      <c r="P131" s="49"/>
-      <c r="Q131" s="49"/>
-      <c r="R131" s="49"/>
-      <c r="S131" s="49"/>
-      <c r="T131" s="49"/>
-      <c r="U131" s="50"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="32"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+      <c r="I131" s="32"/>
+      <c r="J131" s="32"/>
+      <c r="K131" s="32"/>
+      <c r="L131" s="32"/>
+      <c r="M131" s="32"/>
+      <c r="N131" s="32"/>
+      <c r="O131" s="32"/>
+      <c r="P131" s="32"/>
+      <c r="Q131" s="32"/>
+      <c r="R131" s="32"/>
+      <c r="S131" s="32"/>
+      <c r="T131" s="32"/>
+      <c r="U131" s="33"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="39"/>
+      <c r="A132" s="36"/>
       <c r="B132" s="25" t="s">
         <v>180</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="49"/>
-      <c r="E132" s="49"/>
-      <c r="F132" s="49"/>
-      <c r="G132" s="49"/>
-      <c r="H132" s="49"/>
-      <c r="I132" s="49"/>
-      <c r="J132" s="49"/>
-      <c r="K132" s="49"/>
-      <c r="L132" s="49"/>
-      <c r="M132" s="49"/>
-      <c r="N132" s="49"/>
-      <c r="O132" s="49"/>
-      <c r="P132" s="49"/>
-      <c r="Q132" s="49"/>
-      <c r="R132" s="49"/>
-      <c r="S132" s="49"/>
-      <c r="T132" s="49"/>
-      <c r="U132" s="50"/>
+      <c r="D132" s="32"/>
+      <c r="E132" s="32"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="32"/>
+      <c r="H132" s="32"/>
+      <c r="I132" s="32"/>
+      <c r="J132" s="32"/>
+      <c r="K132" s="32"/>
+      <c r="L132" s="32"/>
+      <c r="M132" s="32"/>
+      <c r="N132" s="32"/>
+      <c r="O132" s="32"/>
+      <c r="P132" s="32"/>
+      <c r="Q132" s="32"/>
+      <c r="R132" s="32"/>
+      <c r="S132" s="32"/>
+      <c r="T132" s="32"/>
+      <c r="U132" s="33"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="39"/>
+      <c r="A133" s="36"/>
       <c r="B133" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="49"/>
-      <c r="E133" s="49"/>
-      <c r="F133" s="49"/>
-      <c r="G133" s="49"/>
-      <c r="H133" s="49"/>
-      <c r="I133" s="49"/>
-      <c r="J133" s="49"/>
-      <c r="K133" s="49"/>
-      <c r="L133" s="49"/>
-      <c r="M133" s="49"/>
-      <c r="N133" s="49"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="49"/>
-      <c r="Q133" s="49"/>
-      <c r="R133" s="49"/>
-      <c r="S133" s="49"/>
-      <c r="T133" s="49"/>
-      <c r="U133" s="50"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="32"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+      <c r="I133" s="32"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
+      <c r="L133" s="32"/>
+      <c r="M133" s="32"/>
+      <c r="N133" s="32"/>
+      <c r="O133" s="32"/>
+      <c r="P133" s="32"/>
+      <c r="Q133" s="32"/>
+      <c r="R133" s="32"/>
+      <c r="S133" s="32"/>
+      <c r="T133" s="32"/>
+      <c r="U133" s="33"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="39"/>
+      <c r="A134" s="36"/>
       <c r="B134" s="25" t="s">
         <v>182</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D134" s="49"/>
-      <c r="E134" s="49"/>
-      <c r="F134" s="49"/>
-      <c r="G134" s="49"/>
-      <c r="H134" s="49"/>
-      <c r="I134" s="49"/>
-      <c r="J134" s="49"/>
-      <c r="K134" s="49"/>
-      <c r="L134" s="49"/>
-      <c r="M134" s="49"/>
-      <c r="N134" s="49"/>
-      <c r="O134" s="49"/>
-      <c r="P134" s="49"/>
-      <c r="Q134" s="49"/>
-      <c r="R134" s="49"/>
-      <c r="S134" s="49"/>
-      <c r="T134" s="49"/>
-      <c r="U134" s="50"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
+      <c r="J134" s="32"/>
+      <c r="K134" s="32"/>
+      <c r="L134" s="32"/>
+      <c r="M134" s="32"/>
+      <c r="N134" s="32"/>
+      <c r="O134" s="32"/>
+      <c r="P134" s="32"/>
+      <c r="Q134" s="32"/>
+      <c r="R134" s="32"/>
+      <c r="S134" s="32"/>
+      <c r="T134" s="32"/>
+      <c r="U134" s="33"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="39"/>
+      <c r="A135" s="36"/>
       <c r="B135" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D135" s="49"/>
-      <c r="E135" s="49"/>
-      <c r="F135" s="49"/>
-      <c r="G135" s="49"/>
-      <c r="H135" s="49"/>
-      <c r="I135" s="49"/>
-      <c r="J135" s="49"/>
-      <c r="K135" s="49"/>
-      <c r="L135" s="49"/>
-      <c r="M135" s="49"/>
-      <c r="N135" s="49"/>
-      <c r="O135" s="49"/>
-      <c r="P135" s="49"/>
-      <c r="Q135" s="49"/>
-      <c r="R135" s="49"/>
-      <c r="S135" s="49"/>
-      <c r="T135" s="49"/>
-      <c r="U135" s="50"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="32"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
+      <c r="J135" s="32"/>
+      <c r="K135" s="32"/>
+      <c r="L135" s="32"/>
+      <c r="M135" s="32"/>
+      <c r="N135" s="32"/>
+      <c r="O135" s="32"/>
+      <c r="P135" s="32"/>
+      <c r="Q135" s="32"/>
+      <c r="R135" s="32"/>
+      <c r="S135" s="32"/>
+      <c r="T135" s="32"/>
+      <c r="U135" s="33"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="39"/>
+      <c r="A136" s="36"/>
       <c r="B136" s="25" t="s">
         <v>184</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D136" s="51"/>
-      <c r="E136" s="51"/>
-      <c r="F136" s="51"/>
-      <c r="G136" s="51"/>
-      <c r="H136" s="51"/>
-      <c r="I136" s="51"/>
-      <c r="J136" s="51"/>
-      <c r="K136" s="51"/>
-      <c r="L136" s="51"/>
-      <c r="M136" s="51"/>
-      <c r="N136" s="51"/>
-      <c r="O136" s="51"/>
-      <c r="P136" s="51"/>
-      <c r="Q136" s="51"/>
-      <c r="R136" s="51"/>
-      <c r="S136" s="51"/>
-      <c r="T136" s="51"/>
-      <c r="U136" s="52"/>
+      <c r="D136" s="34"/>
+      <c r="E136" s="34"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="34"/>
+      <c r="H136" s="34"/>
+      <c r="I136" s="34"/>
+      <c r="J136" s="34"/>
+      <c r="K136" s="34"/>
+      <c r="L136" s="34"/>
+      <c r="M136" s="34"/>
+      <c r="N136" s="34"/>
+      <c r="O136" s="34"/>
+      <c r="P136" s="34"/>
+      <c r="Q136" s="34"/>
+      <c r="R136" s="34"/>
+      <c r="S136" s="34"/>
+      <c r="T136" s="34"/>
+      <c r="U136" s="35"/>
     </row>
     <row r="137" spans="1:21" ht="13.9" customHeight="1"/>
     <row r="138" spans="1:21"/>
@@ -6609,26 +6609,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6645,6 +6625,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6687,81 +6687,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29" t="s">
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="41" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29" t="s">
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29" t="s">
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="39">
+      <c r="A4" s="36">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -6815,7 +6815,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="39"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
@@ -6863,7 +6863,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="39"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -6923,7 +6923,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="39"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -6983,7 +6983,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="39"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
@@ -7027,7 +7027,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="39"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
@@ -7079,7 +7079,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="39"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
@@ -7123,7 +7123,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="37">
         <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -7183,7 +7183,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="40"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
@@ -7229,7 +7229,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="12" t="s">
         <v>51</v>
       </c>
@@ -7284,7 +7284,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
@@ -7327,7 +7327,7 @@
       <c r="U14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="12" t="s">
         <v>56</v>
       </c>
@@ -7356,7 +7356,7 @@
       <c r="U15" s="15"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="12" t="s">
         <v>57</v>
       </c>
@@ -7391,7 +7391,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="12" t="s">
         <v>58</v>
       </c>
@@ -7418,7 +7418,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="39">
+      <c r="A18" s="36">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -7463,7 +7463,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
@@ -7494,7 +7494,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
@@ -7549,7 +7549,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -7592,7 +7592,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
@@ -7621,7 +7621,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="39"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="39"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="16" t="s">
         <v>65</v>
       </c>
@@ -7675,7 +7675,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="40">
+      <c r="A25" s="37">
         <v>4</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -7720,7 +7720,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="40"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="12" t="s">
         <v>67</v>
       </c>
@@ -7751,7 +7751,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="40"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="12" t="s">
         <v>68</v>
       </c>
@@ -7806,7 +7806,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="40"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="12" t="s">
         <v>69</v>
       </c>
@@ -7849,90 +7849,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="40"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="20" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="32"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="41"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="40"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="20" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="44"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="40"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="38"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="47"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="39">
+      <c r="A32" s="36">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -7977,7 +7977,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="39"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>44</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>43</v>
@@ -8000,7 +8000,7 @@
         <v>44</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>16</v>
@@ -8020,7 +8020,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="39"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
@@ -8063,117 +8063,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="39"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="32"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="41"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="39"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="22" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="35"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="44"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="39"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="22" t="s">
         <v>81</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="35"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="44"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="39"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="22" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="35"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="44"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="40">
+      <c r="A39" s="37">
         <v>6</v>
       </c>
       <c r="B39" s="22" t="s">
@@ -8182,81 +8182,81 @@
       <c r="C39" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="35"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="44"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="40"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="22" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="33"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="35"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="44"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="40"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="22" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="38"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="47"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="40"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="23" t="s">
         <v>86</v>
       </c>
@@ -8299,9 +8299,9 @@
       <c r="U42" s="15"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="40"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>36</v>
@@ -8340,9 +8340,9 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="40"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>41</v>
@@ -8367,7 +8367,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="40"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="23" t="s">
         <v>90</v>
       </c>
@@ -8394,7 +8394,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="39">
+      <c r="A46" s="36">
         <v>7</v>
       </c>
       <c r="B46" s="25" t="s">
@@ -8439,7 +8439,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="39"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="25" t="s">
         <v>92</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>44</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>43</v>
@@ -8462,7 +8462,7 @@
         <v>44</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>16</v>
@@ -8482,7 +8482,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="39"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="25" t="s">
         <v>93</v>
       </c>
@@ -8525,7 +8525,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="39"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="25" t="s">
         <v>94</v>
       </c>
@@ -8568,7 +8568,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="39"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
@@ -8609,7 +8609,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="39"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="25" t="s">
         <v>96</v>
       </c>
@@ -8644,7 +8644,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="39"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="25" t="s">
         <v>97</v>
       </c>
@@ -8671,7 +8671,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="40">
+      <c r="A53" s="37">
         <v>8</v>
       </c>
       <c r="B53" s="23" t="s">
@@ -8716,7 +8716,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="40"/>
+      <c r="A54" s="37"/>
       <c r="B54" s="23" t="s">
         <v>99</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>44</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>43</v>
@@ -8739,7 +8739,7 @@
         <v>44</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>16</v>
@@ -8759,7 +8759,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="40"/>
+      <c r="A55" s="37"/>
       <c r="B55" s="23" t="s">
         <v>100</v>
       </c>
@@ -8814,7 +8814,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="40"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="23" t="s">
         <v>101</v>
       </c>
@@ -8857,7 +8857,7 @@
       <c r="U56" s="15"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="40"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="23" t="s">
         <v>102</v>
       </c>
@@ -8900,7 +8900,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="40"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="23" t="s">
         <v>103</v>
       </c>
@@ -8935,7 +8935,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="40"/>
+      <c r="A59" s="37"/>
       <c r="B59" s="23" t="s">
         <v>104</v>
       </c>
@@ -8962,7 +8962,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="39">
+      <c r="A60" s="36">
         <v>9</v>
       </c>
       <c r="B60" s="25" t="s">
@@ -9007,7 +9007,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="39"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="25" t="s">
         <v>106</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>44</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>43</v>
@@ -9030,7 +9030,7 @@
         <v>44</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>16</v>
@@ -9050,7 +9050,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="39"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="25" t="s">
         <v>107</v>
       </c>
@@ -9105,7 +9105,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="39"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="25" t="s">
         <v>108</v>
       </c>
@@ -9148,7 +9148,7 @@
       <c r="U63" s="26"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="39"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="25" t="s">
         <v>109</v>
       </c>
@@ -9191,7 +9191,7 @@
       <c r="U64" s="26"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="39"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="25" t="s">
         <v>110</v>
       </c>
@@ -9226,7 +9226,7 @@
       <c r="U65" s="26"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="39"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="25" t="s">
         <v>111</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="U66" s="26"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="40">
+      <c r="A67" s="37">
         <v>10</v>
       </c>
       <c r="B67" s="23" t="s">
@@ -9298,7 +9298,7 @@
       <c r="U67" s="27"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="40"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="23" t="s">
         <v>113</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>44</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>43</v>
@@ -9321,7 +9321,7 @@
         <v>44</v>
       </c>
       <c r="I68" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J68" s="12" t="s">
         <v>16</v>
@@ -9341,7 +9341,7 @@
       <c r="U68" s="27"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="40"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="23" t="s">
         <v>114</v>
       </c>
@@ -9384,7 +9384,7 @@
       <c r="U69" s="27"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="40"/>
+      <c r="A70" s="37"/>
       <c r="B70" s="23" t="s">
         <v>115</v>
       </c>
@@ -9427,7 +9427,7 @@
       <c r="U70" s="27"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="40"/>
+      <c r="A71" s="37"/>
       <c r="B71" s="23" t="s">
         <v>116</v>
       </c>
@@ -9470,7 +9470,7 @@
       <c r="U71" s="27"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="40"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="23" t="s">
         <v>117</v>
       </c>
@@ -9497,7 +9497,7 @@
       <c r="U72" s="27"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="40"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="23" t="s">
         <v>118</v>
       </c>
@@ -9524,7 +9524,7 @@
       <c r="U73" s="27"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="39">
+      <c r="A74" s="36">
         <v>11</v>
       </c>
       <c r="B74" s="25" t="s">
@@ -9569,7 +9569,7 @@
       <c r="U74" s="26"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="39"/>
+      <c r="A75" s="36"/>
       <c r="B75" s="25" t="s">
         <v>120</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>44</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>43</v>
@@ -9592,7 +9592,7 @@
         <v>44</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J75" s="6" t="s">
         <v>16</v>
@@ -9612,7 +9612,7 @@
       <c r="U75" s="26"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="39"/>
+      <c r="A76" s="36"/>
       <c r="B76" s="25" t="s">
         <v>121</v>
       </c>
@@ -9667,7 +9667,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="39"/>
+      <c r="A77" s="36"/>
       <c r="B77" s="25" t="s">
         <v>122</v>
       </c>
@@ -9710,7 +9710,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="39"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="25" t="s">
         <v>123</v>
       </c>
@@ -9753,7 +9753,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="39"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="25" t="s">
         <v>124</v>
       </c>
@@ -9780,7 +9780,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="39"/>
+      <c r="A80" s="36"/>
       <c r="B80" s="25" t="s">
         <v>125</v>
       </c>
@@ -9807,7 +9807,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="40">
+      <c r="A81" s="37">
         <v>12</v>
       </c>
       <c r="B81" s="23" t="s">
@@ -9852,7 +9852,7 @@
       <c r="U81" s="15"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="40"/>
+      <c r="A82" s="37"/>
       <c r="B82" s="23" t="s">
         <v>127</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>44</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>43</v>
@@ -9875,7 +9875,7 @@
         <v>44</v>
       </c>
       <c r="I82" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J82" s="12" t="s">
         <v>16</v>
@@ -9895,7 +9895,7 @@
       <c r="U82" s="15"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="40"/>
+      <c r="A83" s="37"/>
       <c r="B83" s="23" t="s">
         <v>128</v>
       </c>
@@ -9950,7 +9950,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="40"/>
+      <c r="A84" s="37"/>
       <c r="B84" s="23" t="s">
         <v>131</v>
       </c>
@@ -9993,7 +9993,7 @@
       <c r="U84" s="15"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="40"/>
+      <c r="A85" s="37"/>
       <c r="B85" s="23" t="s">
         <v>132</v>
       </c>
@@ -10036,7 +10036,7 @@
       <c r="U85" s="15"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="40"/>
+      <c r="A86" s="37"/>
       <c r="B86" s="23" t="s">
         <v>133</v>
       </c>
@@ -10071,7 +10071,7 @@
       <c r="U86" s="15"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="40"/>
+      <c r="A87" s="37"/>
       <c r="B87" s="23" t="s">
         <v>134</v>
       </c>
@@ -10098,7 +10098,7 @@
       <c r="U87" s="15"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="39">
+      <c r="A88" s="36">
         <v>13</v>
       </c>
       <c r="B88" s="25" t="s">
@@ -10143,7 +10143,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="39"/>
+      <c r="A89" s="36"/>
       <c r="B89" s="25" t="s">
         <v>136</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>44</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>43</v>
@@ -10166,7 +10166,7 @@
         <v>44</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J89" s="6" t="s">
         <v>16</v>
@@ -10186,7 +10186,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="39"/>
+      <c r="A90" s="36"/>
       <c r="B90" s="25" t="s">
         <v>137</v>
       </c>
@@ -10241,7 +10241,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="39"/>
+      <c r="A91" s="36"/>
       <c r="B91" s="25" t="s">
         <v>138</v>
       </c>
@@ -10284,7 +10284,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="39"/>
+      <c r="A92" s="36"/>
       <c r="B92" s="25" t="s">
         <v>139</v>
       </c>
@@ -10327,7 +10327,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="39"/>
+      <c r="A93" s="36"/>
       <c r="B93" s="25" t="s">
         <v>140</v>
       </c>
@@ -10362,7 +10362,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="39"/>
+      <c r="A94" s="36"/>
       <c r="B94" s="25" t="s">
         <v>141</v>
       </c>
@@ -10389,7 +10389,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="40">
+      <c r="A95" s="37">
         <v>14</v>
       </c>
       <c r="B95" s="23" t="s">
@@ -10434,7 +10434,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="40"/>
+      <c r="A96" s="37"/>
       <c r="B96" s="23" t="s">
         <v>143</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>44</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>43</v>
@@ -10457,7 +10457,7 @@
         <v>44</v>
       </c>
       <c r="I96" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J96" s="12" t="s">
         <v>16</v>
@@ -10489,7 +10489,7 @@
       </c>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="40"/>
+      <c r="A97" s="37"/>
       <c r="B97" s="23" t="s">
         <v>144</v>
       </c>
@@ -10532,7 +10532,7 @@
       <c r="U97" s="15"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="40"/>
+      <c r="A98" s="37"/>
       <c r="B98" s="23" t="s">
         <v>145</v>
       </c>
@@ -10575,7 +10575,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="40"/>
+      <c r="A99" s="37"/>
       <c r="B99" s="23" t="s">
         <v>146</v>
       </c>
@@ -10618,7 +10618,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="40"/>
+      <c r="A100" s="37"/>
       <c r="B100" s="23" t="s">
         <v>147</v>
       </c>
@@ -10645,7 +10645,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="40"/>
+      <c r="A101" s="37"/>
       <c r="B101" s="23" t="s">
         <v>148</v>
       </c>
@@ -10672,7 +10672,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="39">
+      <c r="A102" s="36">
         <v>15</v>
       </c>
       <c r="B102" s="25" t="s">
@@ -10717,7 +10717,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="39"/>
+      <c r="A103" s="36"/>
       <c r="B103" s="25" t="s">
         <v>150</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>44</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>43</v>
@@ -10740,7 +10740,7 @@
         <v>44</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J103" s="6" t="s">
         <v>16</v>
@@ -10760,7 +10760,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="39"/>
+      <c r="A104" s="36"/>
       <c r="B104" s="25" t="s">
         <v>151</v>
       </c>
@@ -10815,7 +10815,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="39"/>
+      <c r="A105" s="36"/>
       <c r="B105" s="25" t="s">
         <v>152</v>
       </c>
@@ -10858,7 +10858,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="39"/>
+      <c r="A106" s="36"/>
       <c r="B106" s="25" t="s">
         <v>153</v>
       </c>
@@ -10901,7 +10901,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="39"/>
+      <c r="A107" s="36"/>
       <c r="B107" s="25" t="s">
         <v>154</v>
       </c>
@@ -10936,7 +10936,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="39"/>
+      <c r="A108" s="36"/>
       <c r="B108" s="25" t="s">
         <v>155</v>
       </c>
@@ -10963,7 +10963,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="40">
+      <c r="A109" s="37">
         <v>16</v>
       </c>
       <c r="B109" s="23" t="s">
@@ -11008,7 +11008,7 @@
       <c r="U109" s="27"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="40"/>
+      <c r="A110" s="37"/>
       <c r="B110" s="23" t="s">
         <v>157</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>44</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G110" s="12" t="s">
         <v>43</v>
@@ -11031,7 +11031,7 @@
         <v>44</v>
       </c>
       <c r="I110" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J110" s="12" t="s">
         <v>16</v>
@@ -11051,7 +11051,7 @@
       <c r="U110" s="27"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="40"/>
+      <c r="A111" s="37"/>
       <c r="B111" s="23" t="s">
         <v>158</v>
       </c>
@@ -11106,7 +11106,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="40"/>
+      <c r="A112" s="37"/>
       <c r="B112" s="23" t="s">
         <v>159</v>
       </c>
@@ -11149,7 +11149,7 @@
       <c r="U112" s="27"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="40"/>
+      <c r="A113" s="37"/>
       <c r="B113" s="23" t="s">
         <v>160</v>
       </c>
@@ -11192,7 +11192,7 @@
       <c r="U113" s="27"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="40"/>
+      <c r="A114" s="37"/>
       <c r="B114" s="23" t="s">
         <v>161</v>
       </c>
@@ -11219,7 +11219,7 @@
       <c r="U114" s="27"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="40"/>
+      <c r="A115" s="37"/>
       <c r="B115" s="23" t="s">
         <v>162</v>
       </c>
@@ -11246,7 +11246,7 @@
       <c r="U115" s="27"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="39">
+      <c r="A116" s="36">
         <v>17</v>
       </c>
       <c r="B116" s="25" t="s">
@@ -11289,7 +11289,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="39"/>
+      <c r="A117" s="36"/>
       <c r="B117" s="25" t="s">
         <v>164</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>44</v>
       </c>
       <c r="F117" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>43</v>
@@ -11312,7 +11312,7 @@
         <v>44</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J117" s="6"/>
       <c r="K117" s="8"/>
@@ -11330,7 +11330,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="39"/>
+      <c r="A118" s="36"/>
       <c r="B118" s="25" t="s">
         <v>165</v>
       </c>
@@ -11371,7 +11371,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="39"/>
+      <c r="A119" s="36"/>
       <c r="B119" s="25" t="s">
         <v>166</v>
       </c>
@@ -11412,7 +11412,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="39"/>
+      <c r="A120" s="36"/>
       <c r="B120" s="25" t="s">
         <v>167</v>
       </c>
@@ -11455,7 +11455,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="39"/>
+      <c r="A121" s="36"/>
       <c r="B121" s="25" t="s">
         <v>168</v>
       </c>
@@ -11482,7 +11482,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="39"/>
+      <c r="A122" s="36"/>
       <c r="B122" s="25" t="s">
         <v>169</v>
       </c>
@@ -11509,7 +11509,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="39">
+      <c r="A123" s="36">
         <v>18</v>
       </c>
       <c r="B123" s="25" t="s">
@@ -11518,191 +11518,191 @@
       <c r="C123" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="46" t="s">
+      <c r="D123" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="47"/>
-      <c r="L123" s="47"/>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
-      <c r="O123" s="47"/>
-      <c r="P123" s="47"/>
-      <c r="Q123" s="47"/>
-      <c r="R123" s="47"/>
-      <c r="S123" s="47"/>
-      <c r="T123" s="47"/>
-      <c r="U123" s="48"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="30"/>
+      <c r="K123" s="30"/>
+      <c r="L123" s="30"/>
+      <c r="M123" s="30"/>
+      <c r="N123" s="30"/>
+      <c r="O123" s="30"/>
+      <c r="P123" s="30"/>
+      <c r="Q123" s="30"/>
+      <c r="R123" s="30"/>
+      <c r="S123" s="30"/>
+      <c r="T123" s="30"/>
+      <c r="U123" s="31"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="39"/>
+      <c r="A124" s="36"/>
       <c r="B124" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C124" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="49"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="49"/>
-      <c r="H124" s="49"/>
-      <c r="I124" s="49"/>
-      <c r="J124" s="49"/>
-      <c r="K124" s="49"/>
-      <c r="L124" s="49"/>
-      <c r="M124" s="49"/>
-      <c r="N124" s="49"/>
-      <c r="O124" s="49"/>
-      <c r="P124" s="49"/>
-      <c r="Q124" s="49"/>
-      <c r="R124" s="49"/>
-      <c r="S124" s="49"/>
-      <c r="T124" s="49"/>
-      <c r="U124" s="50"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="32"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+      <c r="I124" s="32"/>
+      <c r="J124" s="32"/>
+      <c r="K124" s="32"/>
+      <c r="L124" s="32"/>
+      <c r="M124" s="32"/>
+      <c r="N124" s="32"/>
+      <c r="O124" s="32"/>
+      <c r="P124" s="32"/>
+      <c r="Q124" s="32"/>
+      <c r="R124" s="32"/>
+      <c r="S124" s="32"/>
+      <c r="T124" s="32"/>
+      <c r="U124" s="33"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="39"/>
+      <c r="A125" s="36"/>
       <c r="B125" s="25" t="s">
         <v>173</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="49"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="49"/>
-      <c r="J125" s="49"/>
-      <c r="K125" s="49"/>
-      <c r="L125" s="49"/>
-      <c r="M125" s="49"/>
-      <c r="N125" s="49"/>
-      <c r="O125" s="49"/>
-      <c r="P125" s="49"/>
-      <c r="Q125" s="49"/>
-      <c r="R125" s="49"/>
-      <c r="S125" s="49"/>
-      <c r="T125" s="49"/>
-      <c r="U125" s="50"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
+      <c r="F125" s="32"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+      <c r="I125" s="32"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="32"/>
+      <c r="L125" s="32"/>
+      <c r="M125" s="32"/>
+      <c r="N125" s="32"/>
+      <c r="O125" s="32"/>
+      <c r="P125" s="32"/>
+      <c r="Q125" s="32"/>
+      <c r="R125" s="32"/>
+      <c r="S125" s="32"/>
+      <c r="T125" s="32"/>
+      <c r="U125" s="33"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="39"/>
+      <c r="A126" s="36"/>
       <c r="B126" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="49"/>
-      <c r="J126" s="49"/>
-      <c r="K126" s="49"/>
-      <c r="L126" s="49"/>
-      <c r="M126" s="49"/>
-      <c r="N126" s="49"/>
-      <c r="O126" s="49"/>
-      <c r="P126" s="49"/>
-      <c r="Q126" s="49"/>
-      <c r="R126" s="49"/>
-      <c r="S126" s="49"/>
-      <c r="T126" s="49"/>
-      <c r="U126" s="50"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
+      <c r="J126" s="32"/>
+      <c r="K126" s="32"/>
+      <c r="L126" s="32"/>
+      <c r="M126" s="32"/>
+      <c r="N126" s="32"/>
+      <c r="O126" s="32"/>
+      <c r="P126" s="32"/>
+      <c r="Q126" s="32"/>
+      <c r="R126" s="32"/>
+      <c r="S126" s="32"/>
+      <c r="T126" s="32"/>
+      <c r="U126" s="33"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="39"/>
+      <c r="A127" s="36"/>
       <c r="B127" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C127" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="49"/>
-      <c r="J127" s="49"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="49"/>
-      <c r="M127" s="49"/>
-      <c r="N127" s="49"/>
-      <c r="O127" s="49"/>
-      <c r="P127" s="49"/>
-      <c r="Q127" s="49"/>
-      <c r="R127" s="49"/>
-      <c r="S127" s="49"/>
-      <c r="T127" s="49"/>
-      <c r="U127" s="50"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="32"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+      <c r="I127" s="32"/>
+      <c r="J127" s="32"/>
+      <c r="K127" s="32"/>
+      <c r="L127" s="32"/>
+      <c r="M127" s="32"/>
+      <c r="N127" s="32"/>
+      <c r="O127" s="32"/>
+      <c r="P127" s="32"/>
+      <c r="Q127" s="32"/>
+      <c r="R127" s="32"/>
+      <c r="S127" s="32"/>
+      <c r="T127" s="32"/>
+      <c r="U127" s="33"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="39"/>
+      <c r="A128" s="36"/>
       <c r="B128" s="25" t="s">
         <v>176</v>
       </c>
       <c r="C128" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="49"/>
-      <c r="F128" s="49"/>
-      <c r="G128" s="49"/>
-      <c r="H128" s="49"/>
-      <c r="I128" s="49"/>
-      <c r="J128" s="49"/>
-      <c r="K128" s="49"/>
-      <c r="L128" s="49"/>
-      <c r="M128" s="49"/>
-      <c r="N128" s="49"/>
-      <c r="O128" s="49"/>
-      <c r="P128" s="49"/>
-      <c r="Q128" s="49"/>
-      <c r="R128" s="49"/>
-      <c r="S128" s="49"/>
-      <c r="T128" s="49"/>
-      <c r="U128" s="50"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="32"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+      <c r="I128" s="32"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="32"/>
+      <c r="L128" s="32"/>
+      <c r="M128" s="32"/>
+      <c r="N128" s="32"/>
+      <c r="O128" s="32"/>
+      <c r="P128" s="32"/>
+      <c r="Q128" s="32"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="32"/>
+      <c r="T128" s="32"/>
+      <c r="U128" s="33"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="39"/>
+      <c r="A129" s="36"/>
       <c r="B129" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C129" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="49"/>
-      <c r="F129" s="49"/>
-      <c r="G129" s="49"/>
-      <c r="H129" s="49"/>
-      <c r="I129" s="49"/>
-      <c r="J129" s="49"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="49"/>
-      <c r="M129" s="49"/>
-      <c r="N129" s="49"/>
-      <c r="O129" s="49"/>
-      <c r="P129" s="49"/>
-      <c r="Q129" s="49"/>
-      <c r="R129" s="49"/>
-      <c r="S129" s="49"/>
-      <c r="T129" s="49"/>
-      <c r="U129" s="50"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="32"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="32"/>
+      <c r="H129" s="32"/>
+      <c r="I129" s="32"/>
+      <c r="J129" s="32"/>
+      <c r="K129" s="32"/>
+      <c r="L129" s="32"/>
+      <c r="M129" s="32"/>
+      <c r="N129" s="32"/>
+      <c r="O129" s="32"/>
+      <c r="P129" s="32"/>
+      <c r="Q129" s="32"/>
+      <c r="R129" s="32"/>
+      <c r="S129" s="32"/>
+      <c r="T129" s="32"/>
+      <c r="U129" s="33"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="39">
+      <c r="A130" s="36">
         <v>19</v>
       </c>
       <c r="B130" s="25" t="s">
@@ -11711,186 +11711,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="49"/>
-      <c r="F130" s="49"/>
-      <c r="G130" s="49"/>
-      <c r="H130" s="49"/>
-      <c r="I130" s="49"/>
-      <c r="J130" s="49"/>
-      <c r="K130" s="49"/>
-      <c r="L130" s="49"/>
-      <c r="M130" s="49"/>
-      <c r="N130" s="49"/>
-      <c r="O130" s="49"/>
-      <c r="P130" s="49"/>
-      <c r="Q130" s="49"/>
-      <c r="R130" s="49"/>
-      <c r="S130" s="49"/>
-      <c r="T130" s="49"/>
-      <c r="U130" s="50"/>
+      <c r="D130" s="32"/>
+      <c r="E130" s="32"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="32"/>
+      <c r="H130" s="32"/>
+      <c r="I130" s="32"/>
+      <c r="J130" s="32"/>
+      <c r="K130" s="32"/>
+      <c r="L130" s="32"/>
+      <c r="M130" s="32"/>
+      <c r="N130" s="32"/>
+      <c r="O130" s="32"/>
+      <c r="P130" s="32"/>
+      <c r="Q130" s="32"/>
+      <c r="R130" s="32"/>
+      <c r="S130" s="32"/>
+      <c r="T130" s="32"/>
+      <c r="U130" s="33"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="39"/>
+      <c r="A131" s="36"/>
       <c r="B131" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="49"/>
-      <c r="E131" s="49"/>
-      <c r="F131" s="49"/>
-      <c r="G131" s="49"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="49"/>
-      <c r="J131" s="49"/>
-      <c r="K131" s="49"/>
-      <c r="L131" s="49"/>
-      <c r="M131" s="49"/>
-      <c r="N131" s="49"/>
-      <c r="O131" s="49"/>
-      <c r="P131" s="49"/>
-      <c r="Q131" s="49"/>
-      <c r="R131" s="49"/>
-      <c r="S131" s="49"/>
-      <c r="T131" s="49"/>
-      <c r="U131" s="50"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="32"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+      <c r="I131" s="32"/>
+      <c r="J131" s="32"/>
+      <c r="K131" s="32"/>
+      <c r="L131" s="32"/>
+      <c r="M131" s="32"/>
+      <c r="N131" s="32"/>
+      <c r="O131" s="32"/>
+      <c r="P131" s="32"/>
+      <c r="Q131" s="32"/>
+      <c r="R131" s="32"/>
+      <c r="S131" s="32"/>
+      <c r="T131" s="32"/>
+      <c r="U131" s="33"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="39"/>
+      <c r="A132" s="36"/>
       <c r="B132" s="25" t="s">
         <v>180</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="49"/>
-      <c r="E132" s="49"/>
-      <c r="F132" s="49"/>
-      <c r="G132" s="49"/>
-      <c r="H132" s="49"/>
-      <c r="I132" s="49"/>
-      <c r="J132" s="49"/>
-      <c r="K132" s="49"/>
-      <c r="L132" s="49"/>
-      <c r="M132" s="49"/>
-      <c r="N132" s="49"/>
-      <c r="O132" s="49"/>
-      <c r="P132" s="49"/>
-      <c r="Q132" s="49"/>
-      <c r="R132" s="49"/>
-      <c r="S132" s="49"/>
-      <c r="T132" s="49"/>
-      <c r="U132" s="50"/>
+      <c r="D132" s="32"/>
+      <c r="E132" s="32"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="32"/>
+      <c r="H132" s="32"/>
+      <c r="I132" s="32"/>
+      <c r="J132" s="32"/>
+      <c r="K132" s="32"/>
+      <c r="L132" s="32"/>
+      <c r="M132" s="32"/>
+      <c r="N132" s="32"/>
+      <c r="O132" s="32"/>
+      <c r="P132" s="32"/>
+      <c r="Q132" s="32"/>
+      <c r="R132" s="32"/>
+      <c r="S132" s="32"/>
+      <c r="T132" s="32"/>
+      <c r="U132" s="33"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="39"/>
+      <c r="A133" s="36"/>
       <c r="B133" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="49"/>
-      <c r="E133" s="49"/>
-      <c r="F133" s="49"/>
-      <c r="G133" s="49"/>
-      <c r="H133" s="49"/>
-      <c r="I133" s="49"/>
-      <c r="J133" s="49"/>
-      <c r="K133" s="49"/>
-      <c r="L133" s="49"/>
-      <c r="M133" s="49"/>
-      <c r="N133" s="49"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="49"/>
-      <c r="Q133" s="49"/>
-      <c r="R133" s="49"/>
-      <c r="S133" s="49"/>
-      <c r="T133" s="49"/>
-      <c r="U133" s="50"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="32"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+      <c r="I133" s="32"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
+      <c r="L133" s="32"/>
+      <c r="M133" s="32"/>
+      <c r="N133" s="32"/>
+      <c r="O133" s="32"/>
+      <c r="P133" s="32"/>
+      <c r="Q133" s="32"/>
+      <c r="R133" s="32"/>
+      <c r="S133" s="32"/>
+      <c r="T133" s="32"/>
+      <c r="U133" s="33"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="39"/>
+      <c r="A134" s="36"/>
       <c r="B134" s="25" t="s">
         <v>182</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D134" s="49"/>
-      <c r="E134" s="49"/>
-      <c r="F134" s="49"/>
-      <c r="G134" s="49"/>
-      <c r="H134" s="49"/>
-      <c r="I134" s="49"/>
-      <c r="J134" s="49"/>
-      <c r="K134" s="49"/>
-      <c r="L134" s="49"/>
-      <c r="M134" s="49"/>
-      <c r="N134" s="49"/>
-      <c r="O134" s="49"/>
-      <c r="P134" s="49"/>
-      <c r="Q134" s="49"/>
-      <c r="R134" s="49"/>
-      <c r="S134" s="49"/>
-      <c r="T134" s="49"/>
-      <c r="U134" s="50"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
+      <c r="J134" s="32"/>
+      <c r="K134" s="32"/>
+      <c r="L134" s="32"/>
+      <c r="M134" s="32"/>
+      <c r="N134" s="32"/>
+      <c r="O134" s="32"/>
+      <c r="P134" s="32"/>
+      <c r="Q134" s="32"/>
+      <c r="R134" s="32"/>
+      <c r="S134" s="32"/>
+      <c r="T134" s="32"/>
+      <c r="U134" s="33"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="39"/>
+      <c r="A135" s="36"/>
       <c r="B135" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D135" s="49"/>
-      <c r="E135" s="49"/>
-      <c r="F135" s="49"/>
-      <c r="G135" s="49"/>
-      <c r="H135" s="49"/>
-      <c r="I135" s="49"/>
-      <c r="J135" s="49"/>
-      <c r="K135" s="49"/>
-      <c r="L135" s="49"/>
-      <c r="M135" s="49"/>
-      <c r="N135" s="49"/>
-      <c r="O135" s="49"/>
-      <c r="P135" s="49"/>
-      <c r="Q135" s="49"/>
-      <c r="R135" s="49"/>
-      <c r="S135" s="49"/>
-      <c r="T135" s="49"/>
-      <c r="U135" s="50"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="32"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
+      <c r="J135" s="32"/>
+      <c r="K135" s="32"/>
+      <c r="L135" s="32"/>
+      <c r="M135" s="32"/>
+      <c r="N135" s="32"/>
+      <c r="O135" s="32"/>
+      <c r="P135" s="32"/>
+      <c r="Q135" s="32"/>
+      <c r="R135" s="32"/>
+      <c r="S135" s="32"/>
+      <c r="T135" s="32"/>
+      <c r="U135" s="33"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="39"/>
+      <c r="A136" s="36"/>
       <c r="B136" s="25" t="s">
         <v>184</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D136" s="51"/>
-      <c r="E136" s="51"/>
-      <c r="F136" s="51"/>
-      <c r="G136" s="51"/>
-      <c r="H136" s="51"/>
-      <c r="I136" s="51"/>
-      <c r="J136" s="51"/>
-      <c r="K136" s="51"/>
-      <c r="L136" s="51"/>
-      <c r="M136" s="51"/>
-      <c r="N136" s="51"/>
-      <c r="O136" s="51"/>
-      <c r="P136" s="51"/>
-      <c r="Q136" s="51"/>
-      <c r="R136" s="51"/>
-      <c r="S136" s="51"/>
-      <c r="T136" s="51"/>
-      <c r="U136" s="52"/>
+      <c r="D136" s="34"/>
+      <c r="E136" s="34"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="34"/>
+      <c r="H136" s="34"/>
+      <c r="I136" s="34"/>
+      <c r="J136" s="34"/>
+      <c r="K136" s="34"/>
+      <c r="L136" s="34"/>
+      <c r="M136" s="34"/>
+      <c r="N136" s="34"/>
+      <c r="O136" s="34"/>
+      <c r="P136" s="34"/>
+      <c r="Q136" s="34"/>
+      <c r="R136" s="34"/>
+      <c r="S136" s="34"/>
+      <c r="T136" s="34"/>
+      <c r="U136" s="35"/>
     </row>
     <row r="137" spans="1:21" ht="13.9" customHeight="1"/>
     <row r="138" spans="1:21"/>
@@ -11908,26 +11908,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -11944,6 +11924,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11986,81 +11986,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="50"/>
+      <c r="D2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29" t="s">
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="41" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29" t="s">
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29" t="s">
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29" t="s">
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="39">
+      <c r="A4" s="36">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -12102,7 +12102,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="39"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
@@ -12162,7 +12162,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="39"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -12210,7 +12210,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="39"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -12270,7 +12270,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="39"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
@@ -12326,7 +12326,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="39"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
@@ -12378,7 +12378,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="39"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
@@ -12422,7 +12422,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="40">
+      <c r="A11" s="37">
         <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -12470,7 +12470,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="40"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
@@ -12528,7 +12528,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="12" t="s">
         <v>51</v>
       </c>
@@ -12571,7 +12571,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="12" t="s">
         <v>55</v>
       </c>
@@ -12614,7 +12614,7 @@
       <c r="U14" s="15"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="12" t="s">
         <v>56</v>
       </c>
@@ -12655,7 +12655,7 @@
       <c r="U15" s="15"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="12" t="s">
         <v>57</v>
       </c>
@@ -12690,7 +12690,7 @@
       <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="12" t="s">
         <v>58</v>
       </c>
@@ -12717,7 +12717,7 @@
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="39">
+      <c r="A18" s="36">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -12750,7 +12750,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="6" t="s">
         <v>60</v>
       </c>
@@ -12793,7 +12793,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
@@ -12836,7 +12836,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="6" t="s">
         <v>62</v>
       </c>
@@ -12879,7 +12879,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
@@ -12920,7 +12920,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="39"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
@@ -12947,7 +12947,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="39"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="16" t="s">
         <v>65</v>
       </c>
@@ -12986,7 +12986,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="40">
+      <c r="A25" s="37">
         <v>4</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -13019,7 +13019,7 @@
       <c r="U25" s="15"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="40"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="12" t="s">
         <v>67</v>
       </c>
@@ -13062,7 +13062,7 @@
       <c r="U26" s="15"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="40"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="12" t="s">
         <v>68</v>
       </c>
@@ -13105,7 +13105,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="40"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="12" t="s">
         <v>69</v>
       </c>
@@ -13148,90 +13148,90 @@
       <c r="U28" s="15"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="40"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="20" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="32"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="41"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="40"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="20" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="44"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="40"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="20" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="38"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="47"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="39">
+      <c r="A32" s="36">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -13264,7 +13264,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="39"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
@@ -13307,7 +13307,7 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="39"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
@@ -13350,117 +13350,117 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="39"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="32"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
+      <c r="Q35" s="40"/>
+      <c r="R35" s="40"/>
+      <c r="S35" s="40"/>
+      <c r="T35" s="40"/>
+      <c r="U35" s="41"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="39"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="22" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="35"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="44"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="39"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="22" t="s">
         <v>81</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="35"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+      <c r="M37" s="43"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="43"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="44"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="39"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="22" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="35"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="43"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="44"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="40">
+      <c r="A39" s="37">
         <v>6</v>
       </c>
       <c r="B39" s="22" t="s">
@@ -13469,81 +13469,81 @@
       <c r="C39" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="35"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="43"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="44"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="40"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="22" t="s">
         <v>84</v>
       </c>
       <c r="C40" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="33"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="35"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="43"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="43"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="44"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="40"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="22" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="38"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="47"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="40"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="23" t="s">
         <v>86</v>
       </c>
@@ -13586,9 +13586,9 @@
       <c r="U42" s="15"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="40"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>36</v>
@@ -13627,9 +13627,9 @@
       <c r="U43" s="15"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="40"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>41</v>
@@ -13666,7 +13666,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="40"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="23" t="s">
         <v>90</v>
       </c>
@@ -13693,7 +13693,7 @@
       <c r="U45" s="15"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="39">
+      <c r="A46" s="36">
         <v>7</v>
       </c>
       <c r="B46" s="25" t="s">
@@ -13738,7 +13738,7 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="39"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="25" t="s">
         <v>92</v>
       </c>
@@ -13781,7 +13781,7 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="39"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="25" t="s">
         <v>93</v>
       </c>
@@ -13824,7 +13824,7 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="39"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="25" t="s">
         <v>94</v>
       </c>
@@ -13867,7 +13867,7 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="39"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="25" t="s">
         <v>95</v>
       </c>
@@ -13908,7 +13908,7 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="39"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="25" t="s">
         <v>96</v>
       </c>
@@ -13943,7 +13943,7 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="39"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="25" t="s">
         <v>97</v>
       </c>
@@ -13970,7 +13970,7 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="40">
+      <c r="A53" s="37">
         <v>8</v>
       </c>
       <c r="B53" s="23" t="s">
@@ -14015,7 +14015,7 @@
       <c r="U53" s="15"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="40"/>
+      <c r="A54" s="37"/>
       <c r="B54" s="23" t="s">
         <v>99</v>
       </c>
@@ -14058,7 +14058,7 @@
       <c r="U54" s="15"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="40"/>
+      <c r="A55" s="37"/>
       <c r="B55" s="23" t="s">
         <v>100</v>
       </c>
@@ -14113,7 +14113,7 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="40"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="23" t="s">
         <v>101</v>
       </c>
@@ -14156,7 +14156,7 @@
       <c r="U56" s="15"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="40"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="23" t="s">
         <v>102</v>
       </c>
@@ -14199,7 +14199,7 @@
       <c r="U57" s="15"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="40"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="23" t="s">
         <v>103</v>
       </c>
@@ -14234,7 +14234,7 @@
       <c r="U58" s="15"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="40"/>
+      <c r="A59" s="37"/>
       <c r="B59" s="23" t="s">
         <v>104</v>
       </c>
@@ -14261,7 +14261,7 @@
       <c r="U59" s="15"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="39">
+      <c r="A60" s="36">
         <v>9</v>
       </c>
       <c r="B60" s="25" t="s">
@@ -14306,7 +14306,7 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="39"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="25" t="s">
         <v>106</v>
       </c>
@@ -14349,7 +14349,7 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="39"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="25" t="s">
         <v>107</v>
       </c>
@@ -14404,7 +14404,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="39"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="25" t="s">
         <v>108</v>
       </c>
@@ -14447,7 +14447,7 @@
       <c r="U63" s="26"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="39"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="25" t="s">
         <v>109</v>
       </c>
@@ -14490,7 +14490,7 @@
       <c r="U64" s="26"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="39"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="25" t="s">
         <v>110</v>
       </c>
@@ -14525,7 +14525,7 @@
       <c r="U65" s="26"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="39"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="25" t="s">
         <v>111</v>
       </c>
@@ -14552,7 +14552,7 @@
       <c r="U66" s="26"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="40">
+      <c r="A67" s="37">
         <v>10</v>
       </c>
       <c r="B67" s="23" t="s">
@@ -14597,7 +14597,7 @@
       <c r="U67" s="27"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="40"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="23" t="s">
         <v>113</v>
       </c>
@@ -14640,7 +14640,7 @@
       <c r="U68" s="27"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="40"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="23" t="s">
         <v>114</v>
       </c>
@@ -14683,7 +14683,7 @@
       <c r="U69" s="27"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="40"/>
+      <c r="A70" s="37"/>
       <c r="B70" s="23" t="s">
         <v>115</v>
       </c>
@@ -14726,7 +14726,7 @@
       <c r="U70" s="27"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="40"/>
+      <c r="A71" s="37"/>
       <c r="B71" s="23" t="s">
         <v>116</v>
       </c>
@@ -14769,7 +14769,7 @@
       <c r="U71" s="27"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="40"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="23" t="s">
         <v>117</v>
       </c>
@@ -14796,7 +14796,7 @@
       <c r="U72" s="27"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="40"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="23" t="s">
         <v>118</v>
       </c>
@@ -14823,7 +14823,7 @@
       <c r="U73" s="27"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="39">
+      <c r="A74" s="36">
         <v>11</v>
       </c>
       <c r="B74" s="25" t="s">
@@ -14868,7 +14868,7 @@
       <c r="U74" s="26"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="39"/>
+      <c r="A75" s="36"/>
       <c r="B75" s="25" t="s">
         <v>120</v>
       </c>
@@ -14911,7 +14911,7 @@
       <c r="U75" s="26"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="39"/>
+      <c r="A76" s="36"/>
       <c r="B76" s="25" t="s">
         <v>121</v>
       </c>
@@ -14966,7 +14966,7 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="39"/>
+      <c r="A77" s="36"/>
       <c r="B77" s="25" t="s">
         <v>122</v>
       </c>
@@ -15009,7 +15009,7 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="39"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="25" t="s">
         <v>123</v>
       </c>
@@ -15052,7 +15052,7 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="39"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="25" t="s">
         <v>124</v>
       </c>
@@ -15079,7 +15079,7 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="39"/>
+      <c r="A80" s="36"/>
       <c r="B80" s="25" t="s">
         <v>125</v>
       </c>
@@ -15106,7 +15106,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="40">
+      <c r="A81" s="37">
         <v>12</v>
       </c>
       <c r="B81" s="23" t="s">
@@ -15151,7 +15151,7 @@
       <c r="U81" s="15"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="40"/>
+      <c r="A82" s="37"/>
       <c r="B82" s="23" t="s">
         <v>127</v>
       </c>
@@ -15194,7 +15194,7 @@
       <c r="U82" s="15"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="40"/>
+      <c r="A83" s="37"/>
       <c r="B83" s="23" t="s">
         <v>128</v>
       </c>
@@ -15249,7 +15249,7 @@
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="40"/>
+      <c r="A84" s="37"/>
       <c r="B84" s="23" t="s">
         <v>131</v>
       </c>
@@ -15292,7 +15292,7 @@
       <c r="U84" s="15"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="40"/>
+      <c r="A85" s="37"/>
       <c r="B85" s="23" t="s">
         <v>132</v>
       </c>
@@ -15335,7 +15335,7 @@
       <c r="U85" s="15"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="40"/>
+      <c r="A86" s="37"/>
       <c r="B86" s="23" t="s">
         <v>133</v>
       </c>
@@ -15370,7 +15370,7 @@
       <c r="U86" s="15"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="40"/>
+      <c r="A87" s="37"/>
       <c r="B87" s="23" t="s">
         <v>134</v>
       </c>
@@ -15397,7 +15397,7 @@
       <c r="U87" s="15"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="39">
+      <c r="A88" s="36">
         <v>13</v>
       </c>
       <c r="B88" s="25" t="s">
@@ -15442,7 +15442,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="39"/>
+      <c r="A89" s="36"/>
       <c r="B89" s="25" t="s">
         <v>136</v>
       </c>
@@ -15485,7 +15485,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="39"/>
+      <c r="A90" s="36"/>
       <c r="B90" s="25" t="s">
         <v>137</v>
       </c>
@@ -15540,7 +15540,7 @@
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="39"/>
+      <c r="A91" s="36"/>
       <c r="B91" s="25" t="s">
         <v>138</v>
       </c>
@@ -15583,7 +15583,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="39"/>
+      <c r="A92" s="36"/>
       <c r="B92" s="25" t="s">
         <v>139</v>
       </c>
@@ -15626,7 +15626,7 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="39"/>
+      <c r="A93" s="36"/>
       <c r="B93" s="25" t="s">
         <v>140</v>
       </c>
@@ -15661,7 +15661,7 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="39"/>
+      <c r="A94" s="36"/>
       <c r="B94" s="25" t="s">
         <v>141</v>
       </c>
@@ -15688,7 +15688,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="40">
+      <c r="A95" s="37">
         <v>14</v>
       </c>
       <c r="B95" s="23" t="s">
@@ -15733,7 +15733,7 @@
       <c r="U95" s="15"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="40"/>
+      <c r="A96" s="37"/>
       <c r="B96" s="23" t="s">
         <v>143</v>
       </c>
@@ -15776,7 +15776,7 @@
       <c r="U96" s="15"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="40"/>
+      <c r="A97" s="37"/>
       <c r="B97" s="23" t="s">
         <v>144</v>
       </c>
@@ -15831,7 +15831,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="40"/>
+      <c r="A98" s="37"/>
       <c r="B98" s="23" t="s">
         <v>145</v>
       </c>
@@ -15874,7 +15874,7 @@
       <c r="U98" s="15"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="40"/>
+      <c r="A99" s="37"/>
       <c r="B99" s="23" t="s">
         <v>146</v>
       </c>
@@ -15917,7 +15917,7 @@
       <c r="U99" s="15"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="40"/>
+      <c r="A100" s="37"/>
       <c r="B100" s="23" t="s">
         <v>147</v>
       </c>
@@ -15944,7 +15944,7 @@
       <c r="U100" s="15"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="40"/>
+      <c r="A101" s="37"/>
       <c r="B101" s="23" t="s">
         <v>148</v>
       </c>
@@ -15971,7 +15971,7 @@
       <c r="U101" s="15"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="39">
+      <c r="A102" s="36">
         <v>15</v>
       </c>
       <c r="B102" s="25" t="s">
@@ -16016,7 +16016,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="39"/>
+      <c r="A103" s="36"/>
       <c r="B103" s="25" t="s">
         <v>150</v>
       </c>
@@ -16059,7 +16059,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="39"/>
+      <c r="A104" s="36"/>
       <c r="B104" s="25" t="s">
         <v>151</v>
       </c>
@@ -16114,7 +16114,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="39"/>
+      <c r="A105" s="36"/>
       <c r="B105" s="25" t="s">
         <v>152</v>
       </c>
@@ -16157,7 +16157,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="39"/>
+      <c r="A106" s="36"/>
       <c r="B106" s="25" t="s">
         <v>153</v>
       </c>
@@ -16200,7 +16200,7 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="39"/>
+      <c r="A107" s="36"/>
       <c r="B107" s="25" t="s">
         <v>154</v>
       </c>
@@ -16235,7 +16235,7 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="39"/>
+      <c r="A108" s="36"/>
       <c r="B108" s="25" t="s">
         <v>155</v>
       </c>
@@ -16262,7 +16262,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="40">
+      <c r="A109" s="37">
         <v>16</v>
       </c>
       <c r="B109" s="23" t="s">
@@ -16307,7 +16307,7 @@
       <c r="U109" s="27"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="40"/>
+      <c r="A110" s="37"/>
       <c r="B110" s="23" t="s">
         <v>157</v>
       </c>
@@ -16350,7 +16350,7 @@
       <c r="U110" s="27"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="40"/>
+      <c r="A111" s="37"/>
       <c r="B111" s="23" t="s">
         <v>158</v>
       </c>
@@ -16405,7 +16405,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="40"/>
+      <c r="A112" s="37"/>
       <c r="B112" s="23" t="s">
         <v>159</v>
       </c>
@@ -16448,7 +16448,7 @@
       <c r="U112" s="27"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="40"/>
+      <c r="A113" s="37"/>
       <c r="B113" s="23" t="s">
         <v>160</v>
       </c>
@@ -16491,7 +16491,7 @@
       <c r="U113" s="27"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="40"/>
+      <c r="A114" s="37"/>
       <c r="B114" s="23" t="s">
         <v>161</v>
       </c>
@@ -16518,7 +16518,7 @@
       <c r="U114" s="27"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="40"/>
+      <c r="A115" s="37"/>
       <c r="B115" s="23" t="s">
         <v>162</v>
       </c>
@@ -16545,7 +16545,7 @@
       <c r="U115" s="27"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="39">
+      <c r="A116" s="36">
         <v>17</v>
       </c>
       <c r="B116" s="25" t="s">
@@ -16588,7 +16588,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="39"/>
+      <c r="A117" s="36"/>
       <c r="B117" s="25" t="s">
         <v>164</v>
       </c>
@@ -16629,7 +16629,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="39"/>
+      <c r="A118" s="36"/>
       <c r="B118" s="25" t="s">
         <v>165</v>
       </c>
@@ -16682,7 +16682,7 @@
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="39"/>
+      <c r="A119" s="36"/>
       <c r="B119" s="25" t="s">
         <v>166</v>
       </c>
@@ -16711,7 +16711,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="39"/>
+      <c r="A120" s="36"/>
       <c r="B120" s="25" t="s">
         <v>167</v>
       </c>
@@ -16754,7 +16754,7 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="39"/>
+      <c r="A121" s="36"/>
       <c r="B121" s="25" t="s">
         <v>168</v>
       </c>
@@ -16781,7 +16781,7 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="39"/>
+      <c r="A122" s="36"/>
       <c r="B122" s="25" t="s">
         <v>169</v>
       </c>
@@ -16808,7 +16808,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="39">
+      <c r="A123" s="36">
         <v>18</v>
       </c>
       <c r="B123" s="25" t="s">
@@ -16817,191 +16817,191 @@
       <c r="C123" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="46" t="s">
+      <c r="D123" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="47"/>
-      <c r="L123" s="47"/>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
-      <c r="O123" s="47"/>
-      <c r="P123" s="47"/>
-      <c r="Q123" s="47"/>
-      <c r="R123" s="47"/>
-      <c r="S123" s="47"/>
-      <c r="T123" s="47"/>
-      <c r="U123" s="48"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="30"/>
+      <c r="K123" s="30"/>
+      <c r="L123" s="30"/>
+      <c r="M123" s="30"/>
+      <c r="N123" s="30"/>
+      <c r="O123" s="30"/>
+      <c r="P123" s="30"/>
+      <c r="Q123" s="30"/>
+      <c r="R123" s="30"/>
+      <c r="S123" s="30"/>
+      <c r="T123" s="30"/>
+      <c r="U123" s="31"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="39"/>
+      <c r="A124" s="36"/>
       <c r="B124" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C124" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D124" s="49"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="49"/>
-      <c r="H124" s="49"/>
-      <c r="I124" s="49"/>
-      <c r="J124" s="49"/>
-      <c r="K124" s="49"/>
-      <c r="L124" s="49"/>
-      <c r="M124" s="49"/>
-      <c r="N124" s="49"/>
-      <c r="O124" s="49"/>
-      <c r="P124" s="49"/>
-      <c r="Q124" s="49"/>
-      <c r="R124" s="49"/>
-      <c r="S124" s="49"/>
-      <c r="T124" s="49"/>
-      <c r="U124" s="50"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="32"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+      <c r="I124" s="32"/>
+      <c r="J124" s="32"/>
+      <c r="K124" s="32"/>
+      <c r="L124" s="32"/>
+      <c r="M124" s="32"/>
+      <c r="N124" s="32"/>
+      <c r="O124" s="32"/>
+      <c r="P124" s="32"/>
+      <c r="Q124" s="32"/>
+      <c r="R124" s="32"/>
+      <c r="S124" s="32"/>
+      <c r="T124" s="32"/>
+      <c r="U124" s="33"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="39"/>
+      <c r="A125" s="36"/>
       <c r="B125" s="25" t="s">
         <v>173</v>
       </c>
       <c r="C125" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="49"/>
-      <c r="H125" s="49"/>
-      <c r="I125" s="49"/>
-      <c r="J125" s="49"/>
-      <c r="K125" s="49"/>
-      <c r="L125" s="49"/>
-      <c r="M125" s="49"/>
-      <c r="N125" s="49"/>
-      <c r="O125" s="49"/>
-      <c r="P125" s="49"/>
-      <c r="Q125" s="49"/>
-      <c r="R125" s="49"/>
-      <c r="S125" s="49"/>
-      <c r="T125" s="49"/>
-      <c r="U125" s="50"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
+      <c r="F125" s="32"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+      <c r="I125" s="32"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="32"/>
+      <c r="L125" s="32"/>
+      <c r="M125" s="32"/>
+      <c r="N125" s="32"/>
+      <c r="O125" s="32"/>
+      <c r="P125" s="32"/>
+      <c r="Q125" s="32"/>
+      <c r="R125" s="32"/>
+      <c r="S125" s="32"/>
+      <c r="T125" s="32"/>
+      <c r="U125" s="33"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="39"/>
+      <c r="A126" s="36"/>
       <c r="B126" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C126" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="49"/>
-      <c r="H126" s="49"/>
-      <c r="I126" s="49"/>
-      <c r="J126" s="49"/>
-      <c r="K126" s="49"/>
-      <c r="L126" s="49"/>
-      <c r="M126" s="49"/>
-      <c r="N126" s="49"/>
-      <c r="O126" s="49"/>
-      <c r="P126" s="49"/>
-      <c r="Q126" s="49"/>
-      <c r="R126" s="49"/>
-      <c r="S126" s="49"/>
-      <c r="T126" s="49"/>
-      <c r="U126" s="50"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
+      <c r="J126" s="32"/>
+      <c r="K126" s="32"/>
+      <c r="L126" s="32"/>
+      <c r="M126" s="32"/>
+      <c r="N126" s="32"/>
+      <c r="O126" s="32"/>
+      <c r="P126" s="32"/>
+      <c r="Q126" s="32"/>
+      <c r="R126" s="32"/>
+      <c r="S126" s="32"/>
+      <c r="T126" s="32"/>
+      <c r="U126" s="33"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="39"/>
+      <c r="A127" s="36"/>
       <c r="B127" s="22" t="s">
         <v>175</v>
       </c>
       <c r="C127" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="49"/>
-      <c r="F127" s="49"/>
-      <c r="G127" s="49"/>
-      <c r="H127" s="49"/>
-      <c r="I127" s="49"/>
-      <c r="J127" s="49"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="49"/>
-      <c r="M127" s="49"/>
-      <c r="N127" s="49"/>
-      <c r="O127" s="49"/>
-      <c r="P127" s="49"/>
-      <c r="Q127" s="49"/>
-      <c r="R127" s="49"/>
-      <c r="S127" s="49"/>
-      <c r="T127" s="49"/>
-      <c r="U127" s="50"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="32"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+      <c r="I127" s="32"/>
+      <c r="J127" s="32"/>
+      <c r="K127" s="32"/>
+      <c r="L127" s="32"/>
+      <c r="M127" s="32"/>
+      <c r="N127" s="32"/>
+      <c r="O127" s="32"/>
+      <c r="P127" s="32"/>
+      <c r="Q127" s="32"/>
+      <c r="R127" s="32"/>
+      <c r="S127" s="32"/>
+      <c r="T127" s="32"/>
+      <c r="U127" s="33"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="39"/>
+      <c r="A128" s="36"/>
       <c r="B128" s="25" t="s">
         <v>176</v>
       </c>
       <c r="C128" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="49"/>
-      <c r="F128" s="49"/>
-      <c r="G128" s="49"/>
-      <c r="H128" s="49"/>
-      <c r="I128" s="49"/>
-      <c r="J128" s="49"/>
-      <c r="K128" s="49"/>
-      <c r="L128" s="49"/>
-      <c r="M128" s="49"/>
-      <c r="N128" s="49"/>
-      <c r="O128" s="49"/>
-      <c r="P128" s="49"/>
-      <c r="Q128" s="49"/>
-      <c r="R128" s="49"/>
-      <c r="S128" s="49"/>
-      <c r="T128" s="49"/>
-      <c r="U128" s="50"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="32"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+      <c r="I128" s="32"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="32"/>
+      <c r="L128" s="32"/>
+      <c r="M128" s="32"/>
+      <c r="N128" s="32"/>
+      <c r="O128" s="32"/>
+      <c r="P128" s="32"/>
+      <c r="Q128" s="32"/>
+      <c r="R128" s="32"/>
+      <c r="S128" s="32"/>
+      <c r="T128" s="32"/>
+      <c r="U128" s="33"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="39"/>
+      <c r="A129" s="36"/>
       <c r="B129" s="25" t="s">
         <v>177</v>
       </c>
       <c r="C129" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="49"/>
-      <c r="F129" s="49"/>
-      <c r="G129" s="49"/>
-      <c r="H129" s="49"/>
-      <c r="I129" s="49"/>
-      <c r="J129" s="49"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="49"/>
-      <c r="M129" s="49"/>
-      <c r="N129" s="49"/>
-      <c r="O129" s="49"/>
-      <c r="P129" s="49"/>
-      <c r="Q129" s="49"/>
-      <c r="R129" s="49"/>
-      <c r="S129" s="49"/>
-      <c r="T129" s="49"/>
-      <c r="U129" s="50"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="32"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="32"/>
+      <c r="H129" s="32"/>
+      <c r="I129" s="32"/>
+      <c r="J129" s="32"/>
+      <c r="K129" s="32"/>
+      <c r="L129" s="32"/>
+      <c r="M129" s="32"/>
+      <c r="N129" s="32"/>
+      <c r="O129" s="32"/>
+      <c r="P129" s="32"/>
+      <c r="Q129" s="32"/>
+      <c r="R129" s="32"/>
+      <c r="S129" s="32"/>
+      <c r="T129" s="32"/>
+      <c r="U129" s="33"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="39">
+      <c r="A130" s="36">
         <v>19</v>
       </c>
       <c r="B130" s="25" t="s">
@@ -17010,186 +17010,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="49"/>
-      <c r="F130" s="49"/>
-      <c r="G130" s="49"/>
-      <c r="H130" s="49"/>
-      <c r="I130" s="49"/>
-      <c r="J130" s="49"/>
-      <c r="K130" s="49"/>
-      <c r="L130" s="49"/>
-      <c r="M130" s="49"/>
-      <c r="N130" s="49"/>
-      <c r="O130" s="49"/>
-      <c r="P130" s="49"/>
-      <c r="Q130" s="49"/>
-      <c r="R130" s="49"/>
-      <c r="S130" s="49"/>
-      <c r="T130" s="49"/>
-      <c r="U130" s="50"/>
+      <c r="D130" s="32"/>
+      <c r="E130" s="32"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="32"/>
+      <c r="H130" s="32"/>
+      <c r="I130" s="32"/>
+      <c r="J130" s="32"/>
+      <c r="K130" s="32"/>
+      <c r="L130" s="32"/>
+      <c r="M130" s="32"/>
+      <c r="N130" s="32"/>
+      <c r="O130" s="32"/>
+      <c r="P130" s="32"/>
+      <c r="Q130" s="32"/>
+      <c r="R130" s="32"/>
+      <c r="S130" s="32"/>
+      <c r="T130" s="32"/>
+      <c r="U130" s="33"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="39"/>
+      <c r="A131" s="36"/>
       <c r="B131" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="49"/>
-      <c r="E131" s="49"/>
-      <c r="F131" s="49"/>
-      <c r="G131" s="49"/>
-      <c r="H131" s="49"/>
-      <c r="I131" s="49"/>
-      <c r="J131" s="49"/>
-      <c r="K131" s="49"/>
-      <c r="L131" s="49"/>
-      <c r="M131" s="49"/>
-      <c r="N131" s="49"/>
-      <c r="O131" s="49"/>
-      <c r="P131" s="49"/>
-      <c r="Q131" s="49"/>
-      <c r="R131" s="49"/>
-      <c r="S131" s="49"/>
-      <c r="T131" s="49"/>
-      <c r="U131" s="50"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="32"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+      <c r="I131" s="32"/>
+      <c r="J131" s="32"/>
+      <c r="K131" s="32"/>
+      <c r="L131" s="32"/>
+      <c r="M131" s="32"/>
+      <c r="N131" s="32"/>
+      <c r="O131" s="32"/>
+      <c r="P131" s="32"/>
+      <c r="Q131" s="32"/>
+      <c r="R131" s="32"/>
+      <c r="S131" s="32"/>
+      <c r="T131" s="32"/>
+      <c r="U131" s="33"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="39"/>
+      <c r="A132" s="36"/>
       <c r="B132" s="25" t="s">
         <v>180</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="49"/>
-      <c r="E132" s="49"/>
-      <c r="F132" s="49"/>
-      <c r="G132" s="49"/>
-      <c r="H132" s="49"/>
-      <c r="I132" s="49"/>
-      <c r="J132" s="49"/>
-      <c r="K132" s="49"/>
-      <c r="L132" s="49"/>
-      <c r="M132" s="49"/>
-      <c r="N132" s="49"/>
-      <c r="O132" s="49"/>
-      <c r="P132" s="49"/>
-      <c r="Q132" s="49"/>
-      <c r="R132" s="49"/>
-      <c r="S132" s="49"/>
-      <c r="T132" s="49"/>
-      <c r="U132" s="50"/>
+      <c r="D132" s="32"/>
+      <c r="E132" s="32"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="32"/>
+      <c r="H132" s="32"/>
+      <c r="I132" s="32"/>
+      <c r="J132" s="32"/>
+      <c r="K132" s="32"/>
+      <c r="L132" s="32"/>
+      <c r="M132" s="32"/>
+      <c r="N132" s="32"/>
+      <c r="O132" s="32"/>
+      <c r="P132" s="32"/>
+      <c r="Q132" s="32"/>
+      <c r="R132" s="32"/>
+      <c r="S132" s="32"/>
+      <c r="T132" s="32"/>
+      <c r="U132" s="33"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="39"/>
+      <c r="A133" s="36"/>
       <c r="B133" s="25" t="s">
         <v>181</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="49"/>
-      <c r="E133" s="49"/>
-      <c r="F133" s="49"/>
-      <c r="G133" s="49"/>
-      <c r="H133" s="49"/>
-      <c r="I133" s="49"/>
-      <c r="J133" s="49"/>
-      <c r="K133" s="49"/>
-      <c r="L133" s="49"/>
-      <c r="M133" s="49"/>
-      <c r="N133" s="49"/>
-      <c r="O133" s="49"/>
-      <c r="P133" s="49"/>
-      <c r="Q133" s="49"/>
-      <c r="R133" s="49"/>
-      <c r="S133" s="49"/>
-      <c r="T133" s="49"/>
-      <c r="U133" s="50"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="32"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+      <c r="I133" s="32"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
+      <c r="L133" s="32"/>
+      <c r="M133" s="32"/>
+      <c r="N133" s="32"/>
+      <c r="O133" s="32"/>
+      <c r="P133" s="32"/>
+      <c r="Q133" s="32"/>
+      <c r="R133" s="32"/>
+      <c r="S133" s="32"/>
+      <c r="T133" s="32"/>
+      <c r="U133" s="33"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="39"/>
+      <c r="A134" s="36"/>
       <c r="B134" s="25" t="s">
         <v>182</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D134" s="49"/>
-      <c r="E134" s="49"/>
-      <c r="F134" s="49"/>
-      <c r="G134" s="49"/>
-      <c r="H134" s="49"/>
-      <c r="I134" s="49"/>
-      <c r="J134" s="49"/>
-      <c r="K134" s="49"/>
-      <c r="L134" s="49"/>
-      <c r="M134" s="49"/>
-      <c r="N134" s="49"/>
-      <c r="O134" s="49"/>
-      <c r="P134" s="49"/>
-      <c r="Q134" s="49"/>
-      <c r="R134" s="49"/>
-      <c r="S134" s="49"/>
-      <c r="T134" s="49"/>
-      <c r="U134" s="50"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
+      <c r="J134" s="32"/>
+      <c r="K134" s="32"/>
+      <c r="L134" s="32"/>
+      <c r="M134" s="32"/>
+      <c r="N134" s="32"/>
+      <c r="O134" s="32"/>
+      <c r="P134" s="32"/>
+      <c r="Q134" s="32"/>
+      <c r="R134" s="32"/>
+      <c r="S134" s="32"/>
+      <c r="T134" s="32"/>
+      <c r="U134" s="33"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="39"/>
+      <c r="A135" s="36"/>
       <c r="B135" s="25" t="s">
         <v>183</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D135" s="49"/>
-      <c r="E135" s="49"/>
-      <c r="F135" s="49"/>
-      <c r="G135" s="49"/>
-      <c r="H135" s="49"/>
-      <c r="I135" s="49"/>
-      <c r="J135" s="49"/>
-      <c r="K135" s="49"/>
-      <c r="L135" s="49"/>
-      <c r="M135" s="49"/>
-      <c r="N135" s="49"/>
-      <c r="O135" s="49"/>
-      <c r="P135" s="49"/>
-      <c r="Q135" s="49"/>
-      <c r="R135" s="49"/>
-      <c r="S135" s="49"/>
-      <c r="T135" s="49"/>
-      <c r="U135" s="50"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="32"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
+      <c r="J135" s="32"/>
+      <c r="K135" s="32"/>
+      <c r="L135" s="32"/>
+      <c r="M135" s="32"/>
+      <c r="N135" s="32"/>
+      <c r="O135" s="32"/>
+      <c r="P135" s="32"/>
+      <c r="Q135" s="32"/>
+      <c r="R135" s="32"/>
+      <c r="S135" s="32"/>
+      <c r="T135" s="32"/>
+      <c r="U135" s="33"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="39"/>
+      <c r="A136" s="36"/>
       <c r="B136" s="25" t="s">
         <v>184</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D136" s="51"/>
-      <c r="E136" s="51"/>
-      <c r="F136" s="51"/>
-      <c r="G136" s="51"/>
-      <c r="H136" s="51"/>
-      <c r="I136" s="51"/>
-      <c r="J136" s="51"/>
-      <c r="K136" s="51"/>
-      <c r="L136" s="51"/>
-      <c r="M136" s="51"/>
-      <c r="N136" s="51"/>
-      <c r="O136" s="51"/>
-      <c r="P136" s="51"/>
-      <c r="Q136" s="51"/>
-      <c r="R136" s="51"/>
-      <c r="S136" s="51"/>
-      <c r="T136" s="51"/>
-      <c r="U136" s="52"/>
+      <c r="D136" s="34"/>
+      <c r="E136" s="34"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="34"/>
+      <c r="H136" s="34"/>
+      <c r="I136" s="34"/>
+      <c r="J136" s="34"/>
+      <c r="K136" s="34"/>
+      <c r="L136" s="34"/>
+      <c r="M136" s="34"/>
+      <c r="N136" s="34"/>
+      <c r="O136" s="34"/>
+      <c r="P136" s="34"/>
+      <c r="Q136" s="34"/>
+      <c r="R136" s="34"/>
+      <c r="S136" s="34"/>
+      <c r="T136" s="34"/>
+      <c r="U136" s="35"/>
     </row>
     <row r="137" spans="1:21" ht="13.9" customHeight="1"/>
     <row r="138" spans="1:21"/>
@@ -17207,26 +17207,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -17243,6 +17223,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
